--- a/f2_tabelas/tabela_obitos_por_variavel.xlsx
+++ b/f2_tabelas/tabela_obitos_por_variavel.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N24"/>
+  <dimension ref="A1:O24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -425,6 +425,11 @@
           <t>2023</t>
         </is>
       </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -473,6 +478,9 @@
       <c r="N2">
         <v>53</v>
       </c>
+      <c r="O2">
+        <v>44</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -521,6 +529,9 @@
       <c r="N3">
         <v>91</v>
       </c>
+      <c r="O3">
+        <v>76</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -569,6 +580,9 @@
       <c r="N4">
         <v>570</v>
       </c>
+      <c r="O4">
+        <v>479</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -617,6 +631,9 @@
       <c r="N5">
         <v>1927</v>
       </c>
+      <c r="O5">
+        <v>1678</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -665,6 +682,9 @@
       <c r="N6">
         <v>117</v>
       </c>
+      <c r="O6">
+        <v>92</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -713,6 +733,9 @@
       <c r="N7">
         <v>537</v>
       </c>
+      <c r="O7">
+        <v>489</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -761,6 +784,9 @@
       <c r="N8">
         <v>344</v>
       </c>
+      <c r="O8">
+        <v>255</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -809,6 +835,9 @@
       <c r="N9">
         <v>249</v>
       </c>
+      <c r="O9">
+        <v>249</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -857,6 +886,9 @@
       <c r="N10">
         <v>3627</v>
       </c>
+      <c r="O10">
+        <v>3156</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -905,6 +937,9 @@
       <c r="N11">
         <v>228</v>
       </c>
+      <c r="O11">
+        <v>179</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -953,6 +988,9 @@
       <c r="N12">
         <v>8</v>
       </c>
+      <c r="O12">
+        <v>6</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1001,6 +1039,9 @@
       <c r="N13">
         <v>10</v>
       </c>
+      <c r="O13">
+        <v>10</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1049,6 +1090,9 @@
       <c r="N14">
         <v>15</v>
       </c>
+      <c r="O14">
+        <v>11</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1097,6 +1141,9 @@
       <c r="N15">
         <v>2166</v>
       </c>
+      <c r="O15">
+        <v>1953</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1145,6 +1192,9 @@
       <c r="N16">
         <v>1122</v>
       </c>
+      <c r="O16">
+        <v>896</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1193,6 +1243,9 @@
       <c r="N17">
         <v>368</v>
       </c>
+      <c r="O17">
+        <v>326</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1241,6 +1294,9 @@
       <c r="N18">
         <v>97</v>
       </c>
+      <c r="O18">
+        <v>80</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1289,6 +1345,9 @@
       <c r="N19">
         <v>135</v>
       </c>
+      <c r="O19">
+        <v>107</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1337,6 +1396,9 @@
       <c r="N20">
         <v>1650</v>
       </c>
+      <c r="O20">
+        <v>1410</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1385,6 +1447,9 @@
       <c r="N21">
         <v>1040</v>
       </c>
+      <c r="O21">
+        <v>893</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1433,6 +1498,9 @@
       <c r="N22">
         <v>1028</v>
       </c>
+      <c r="O22">
+        <v>923</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1481,6 +1549,9 @@
       <c r="N23">
         <v>79</v>
       </c>
+      <c r="O23">
+        <v>66</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1528,6 +1599,9 @@
       </c>
       <c r="N24">
         <v>91</v>
+      </c>
+      <c r="O24">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
